--- a/Bases_de_Dados/FootyStats/Germany 2. Bundesliga_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Germany 2. Bundesliga_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP213"/>
+  <dimension ref="A1:BP214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AQ9" t="n">
         <v>1.08</v>
@@ -3966,7 +3966,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -6361,7 +6361,7 @@
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AQ27" t="n">
         <v>0.83</v>
@@ -8544,7 +8544,7 @@
         <v>1</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR37" t="n">
         <v>2.02</v>
@@ -10285,7 +10285,7 @@
         <v>0</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AQ45" t="n">
         <v>1.09</v>
@@ -11160,7 +11160,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR49" t="n">
         <v>2</v>
@@ -15956,7 +15956,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ71" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR71" t="n">
         <v>1.55</v>
@@ -16389,7 +16389,7 @@
         <v>2.33</v>
       </c>
       <c r="AP73" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AQ73" t="n">
         <v>1.92</v>
@@ -16828,7 +16828,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ75" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR75" t="n">
         <v>1.96</v>
@@ -18569,7 +18569,7 @@
         <v>0.75</v>
       </c>
       <c r="AP83" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AQ83" t="n">
         <v>0.83</v>
@@ -20970,7 +20970,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ94" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR94" t="n">
         <v>1.67</v>
@@ -22711,7 +22711,7 @@
         <v>0.6</v>
       </c>
       <c r="AP102" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AQ102" t="n">
         <v>0.73</v>
@@ -25330,7 +25330,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ114" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR114" t="n">
         <v>1.38</v>
@@ -27289,7 +27289,7 @@
         <v>0.57</v>
       </c>
       <c r="AP123" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AQ123" t="n">
         <v>0.83</v>
@@ -28600,7 +28600,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ129" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR129" t="n">
         <v>1.34</v>
@@ -30341,7 +30341,7 @@
         <v>1.86</v>
       </c>
       <c r="AP137" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AQ137" t="n">
         <v>1.64</v>
@@ -33614,7 +33614,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ152" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR152" t="n">
         <v>1.34</v>
@@ -35358,7 +35358,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ160" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR160" t="n">
         <v>1.41</v>
@@ -36663,7 +36663,7 @@
         <v>1.13</v>
       </c>
       <c r="AP166" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AQ166" t="n">
         <v>0.91</v>
@@ -38628,7 +38628,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ175" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR175" t="n">
         <v>1.88</v>
@@ -40151,7 +40151,7 @@
         <v>1.3</v>
       </c>
       <c r="AP182" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AQ182" t="n">
         <v>1.33</v>
@@ -43424,7 +43424,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ197" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR197" t="n">
         <v>1.42</v>
@@ -44075,7 +44075,7 @@
         <v>0.91</v>
       </c>
       <c r="AP200" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AQ200" t="n">
         <v>0.83</v>
@@ -46988,6 +46988,224 @@
       </c>
       <c r="BP213" t="n">
         <v>1.48</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" t="n">
+        <v>8227981</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Germany 2. Bundesliga</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="n">
+        <v>46081.6875</v>
+      </c>
+      <c r="F214" t="n">
+        <v>24</v>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Greuther Fürth</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Schalke 04</t>
+        </is>
+      </c>
+      <c r="I214" t="n">
+        <v>1</v>
+      </c>
+      <c r="J214" t="n">
+        <v>0</v>
+      </c>
+      <c r="K214" t="n">
+        <v>1</v>
+      </c>
+      <c r="L214" t="n">
+        <v>1</v>
+      </c>
+      <c r="M214" t="n">
+        <v>1</v>
+      </c>
+      <c r="N214" t="n">
+        <v>2</v>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>['12']</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>['75']</t>
+        </is>
+      </c>
+      <c r="Q214" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="R214" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S214" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T214" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="U214" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="V214" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="W214" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X214" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y214" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z214" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA214" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB214" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC214" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD214" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE214" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF214" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AG214" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH214" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI214" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AJ214" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AK214" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AL214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM214" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN214" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AO214" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AP214" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AQ214" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AR214" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AS214" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AT214" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AU214" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV214" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW214" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX214" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY214" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ214" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA214" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB214" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC214" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD214" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BE214" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="BF214" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BG214" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BH214" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BI214" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BJ214" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BK214" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BL214" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BM214" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BN214" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BO214" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="BP214" t="n">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Germany 2. Bundesliga_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Germany 2. Bundesliga_20252026.xlsx
@@ -46712,13 +46712,13 @@
         <v>1</v>
       </c>
       <c r="AW212" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AX212" t="n">
         <v>5</v>
       </c>
       <c r="AY212" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AZ212" t="n">
         <v>6</v>

--- a/Bases_de_Dados/FootyStats/Germany 2. Bundesliga_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Germany 2. Bundesliga_20252026.xlsx
@@ -46491,7 +46491,7 @@
         <v>2</v>
       </c>
       <c r="AV211" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW211" t="n">
         <v>8</v>
@@ -46503,7 +46503,7 @@
         <v>10</v>
       </c>
       <c r="AZ211" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA211" t="n">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/Germany 2. Bundesliga_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Germany 2. Bundesliga_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP214"/>
+  <dimension ref="A1:BP217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1132,7 +1132,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
         <v>2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ8" t="n">
         <v>0.91</v>
@@ -3745,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ15" t="n">
         <v>0.83</v>
@@ -4617,10 +4617,10 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR19" t="n">
         <v>0</v>
@@ -5056,7 +5056,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR21" t="n">
         <v>0.85</v>
@@ -7015,7 +7015,7 @@
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ30" t="n">
         <v>1.77</v>
@@ -7451,7 +7451,7 @@
         <v>3</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ32" t="n">
         <v>0.83</v>
@@ -7672,7 +7672,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR33" t="n">
         <v>1.91</v>
@@ -7890,7 +7890,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR34" t="n">
         <v>1.04</v>
@@ -8105,7 +8105,7 @@
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ35" t="n">
         <v>0.83</v>
@@ -9198,7 +9198,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR40" t="n">
         <v>1.4</v>
@@ -10724,7 +10724,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR47" t="n">
         <v>1.56</v>
@@ -11157,7 +11157,7 @@
         <v>1.5</v>
       </c>
       <c r="AP49" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ49" t="n">
         <v>1.62</v>
@@ -11375,7 +11375,7 @@
         <v>1</v>
       </c>
       <c r="AP50" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ50" t="n">
         <v>1.75</v>
@@ -11593,7 +11593,7 @@
         <v>1.5</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ51" t="n">
         <v>1.77</v>
@@ -12032,7 +12032,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ53" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR53" t="n">
         <v>1.36</v>
@@ -14645,7 +14645,7 @@
         <v>1.67</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ65" t="n">
         <v>1.75</v>
@@ -14866,7 +14866,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ66" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR66" t="n">
         <v>1.26</v>
@@ -15299,10 +15299,10 @@
         <v>1</v>
       </c>
       <c r="AP68" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ68" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR68" t="n">
         <v>1.11</v>
@@ -15738,7 +15738,7 @@
         <v>1</v>
       </c>
       <c r="AQ70" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR70" t="n">
         <v>1.28</v>
@@ -16171,7 +16171,7 @@
         <v>2</v>
       </c>
       <c r="AP72" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ72" t="n">
         <v>1.77</v>
@@ -18572,7 +18572,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ83" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR83" t="n">
         <v>1.17</v>
@@ -19659,7 +19659,7 @@
         <v>2.25</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ88" t="n">
         <v>0.91</v>
@@ -19877,10 +19877,10 @@
         <v>0.75</v>
       </c>
       <c r="AP89" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ89" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR89" t="n">
         <v>1.69</v>
@@ -20095,7 +20095,7 @@
         <v>2</v>
       </c>
       <c r="AP90" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ90" t="n">
         <v>1.92</v>
@@ -20316,7 +20316,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ91" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR91" t="n">
         <v>1.78</v>
@@ -21185,7 +21185,7 @@
         <v>1</v>
       </c>
       <c r="AP95" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ95" t="n">
         <v>1.08</v>
@@ -22496,7 +22496,7 @@
         <v>1</v>
       </c>
       <c r="AQ101" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR101" t="n">
         <v>1.27</v>
@@ -22714,7 +22714,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ102" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR102" t="n">
         <v>1.28</v>
@@ -23150,7 +23150,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ104" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR104" t="n">
         <v>1.44</v>
@@ -23801,7 +23801,7 @@
         <v>0.17</v>
       </c>
       <c r="AP107" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ107" t="n">
         <v>0.83</v>
@@ -24237,7 +24237,7 @@
         <v>2.2</v>
       </c>
       <c r="AP109" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ109" t="n">
         <v>1.75</v>
@@ -24673,7 +24673,7 @@
         <v>1</v>
       </c>
       <c r="AP111" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ111" t="n">
         <v>0.91</v>
@@ -26420,7 +26420,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ119" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR119" t="n">
         <v>1.95</v>
@@ -27071,7 +27071,7 @@
         <v>1.17</v>
       </c>
       <c r="AP122" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ122" t="n">
         <v>1.09</v>
@@ -27507,10 +27507,10 @@
         <v>1.17</v>
       </c>
       <c r="AP124" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ124" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR124" t="n">
         <v>1.63</v>
@@ -27946,7 +27946,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ126" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR126" t="n">
         <v>1.51</v>
@@ -29472,7 +29472,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ133" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR133" t="n">
         <v>1.71</v>
@@ -29687,7 +29687,7 @@
         <v>0.57</v>
       </c>
       <c r="AP134" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ134" t="n">
         <v>1.33</v>
@@ -30123,7 +30123,7 @@
         <v>1</v>
       </c>
       <c r="AP136" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ136" t="n">
         <v>0.83</v>
@@ -31213,7 +31213,7 @@
         <v>1</v>
       </c>
       <c r="AP141" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ141" t="n">
         <v>0.83</v>
@@ -31652,7 +31652,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ143" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR143" t="n">
         <v>1.81</v>
@@ -31870,7 +31870,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ144" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR144" t="n">
         <v>1.59</v>
@@ -32521,7 +32521,7 @@
         <v>0.71</v>
       </c>
       <c r="AP147" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ147" t="n">
         <v>0.83</v>
@@ -33178,7 +33178,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ150" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR150" t="n">
         <v>1.93</v>
@@ -33611,7 +33611,7 @@
         <v>2</v>
       </c>
       <c r="AP152" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ152" t="n">
         <v>1.62</v>
@@ -34483,7 +34483,7 @@
         <v>1.11</v>
       </c>
       <c r="AP156" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ156" t="n">
         <v>1.33</v>
@@ -35140,7 +35140,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ159" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR159" t="n">
         <v>1.45</v>
@@ -35355,7 +35355,7 @@
         <v>1.78</v>
       </c>
       <c r="AP160" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ160" t="n">
         <v>1.62</v>
@@ -36448,7 +36448,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ165" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR165" t="n">
         <v>1.79</v>
@@ -37317,7 +37317,7 @@
         <v>0.89</v>
       </c>
       <c r="AP169" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ169" t="n">
         <v>1.08</v>
@@ -37538,7 +37538,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ170" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR170" t="n">
         <v>1.83</v>
@@ -38189,7 +38189,7 @@
         <v>1.6</v>
       </c>
       <c r="AP173" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ173" t="n">
         <v>1.92</v>
@@ -38410,7 +38410,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ174" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR174" t="n">
         <v>1.55</v>
@@ -38843,10 +38843,10 @@
         <v>1</v>
       </c>
       <c r="AP176" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ176" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR176" t="n">
         <v>1.29</v>
@@ -39715,7 +39715,7 @@
         <v>1.44</v>
       </c>
       <c r="AP180" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ180" t="n">
         <v>1.25</v>
@@ -40590,7 +40590,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ184" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR184" t="n">
         <v>1.95</v>
@@ -42116,7 +42116,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ191" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR191" t="n">
         <v>1.58</v>
@@ -42334,7 +42334,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ192" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR192" t="n">
         <v>1.39</v>
@@ -42767,7 +42767,7 @@
         <v>1.73</v>
       </c>
       <c r="AP194" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ194" t="n">
         <v>1.92</v>
@@ -42985,7 +42985,7 @@
         <v>1.4</v>
       </c>
       <c r="AP195" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ195" t="n">
         <v>1.25</v>
@@ -43639,7 +43639,7 @@
         <v>0.7</v>
       </c>
       <c r="AP198" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ198" t="n">
         <v>0.83</v>
@@ -44296,7 +44296,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ201" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR201" t="n">
         <v>1.86</v>
@@ -47151,13 +47151,13 @@
         <v>5</v>
       </c>
       <c r="AX214" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY214" t="n">
         <v>6</v>
       </c>
       <c r="AZ214" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA214" t="n">
         <v>4</v>
@@ -47206,6 +47206,660 @@
       </c>
       <c r="BP214" t="n">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="n">
+        <v>214</v>
+      </c>
+      <c r="B215" t="n">
+        <v>8228072</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Germany 2. Bundesliga</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="n">
+        <v>46082.39583333334</v>
+      </c>
+      <c r="F215" t="n">
+        <v>24</v>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Magdeburg</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Karlsruher SC</t>
+        </is>
+      </c>
+      <c r="I215" t="n">
+        <v>0</v>
+      </c>
+      <c r="J215" t="n">
+        <v>1</v>
+      </c>
+      <c r="K215" t="n">
+        <v>1</v>
+      </c>
+      <c r="L215" t="n">
+        <v>1</v>
+      </c>
+      <c r="M215" t="n">
+        <v>3</v>
+      </c>
+      <c r="N215" t="n">
+        <v>4</v>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>['66']</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>['20', '53', '87']</t>
+        </is>
+      </c>
+      <c r="Q215" t="n">
+        <v>2</v>
+      </c>
+      <c r="R215" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="S215" t="n">
+        <v>4</v>
+      </c>
+      <c r="T215" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="U215" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="V215" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="W215" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="X215" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y215" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z215" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AA215" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB215" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="AC215" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD215" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE215" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF215" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG215" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AH215" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AI215" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AJ215" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AK215" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AL215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM215" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AN215" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AO215" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AP215" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AQ215" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR215" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AS215" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AT215" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AU215" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV215" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW215" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX215" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY215" t="n">
+        <v>23</v>
+      </c>
+      <c r="AZ215" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA215" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB215" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC215" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD215" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BE215" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF215" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BG215" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH215" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="BI215" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BJ215" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BK215" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BL215" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BM215" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BN215" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BO215" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BP215" t="n">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="n">
+        <v>215</v>
+      </c>
+      <c r="B216" t="n">
+        <v>8227958</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Germany 2. Bundesliga</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="n">
+        <v>46082.39583333334</v>
+      </c>
+      <c r="F216" t="n">
+        <v>24</v>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Hertha BSC</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Nürnberg</t>
+        </is>
+      </c>
+      <c r="I216" t="n">
+        <v>1</v>
+      </c>
+      <c r="J216" t="n">
+        <v>1</v>
+      </c>
+      <c r="K216" t="n">
+        <v>2</v>
+      </c>
+      <c r="L216" t="n">
+        <v>2</v>
+      </c>
+      <c r="M216" t="n">
+        <v>1</v>
+      </c>
+      <c r="N216" t="n">
+        <v>3</v>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>['20', '88']</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>['45+1']</t>
+        </is>
+      </c>
+      <c r="Q216" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R216" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S216" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T216" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="U216" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="V216" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="W216" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X216" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y216" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z216" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA216" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB216" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AC216" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD216" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE216" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF216" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AG216" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AH216" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AI216" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ216" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AK216" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL216" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM216" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN216" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO216" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AP216" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AQ216" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AR216" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AS216" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AT216" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AU216" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV216" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW216" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX216" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY216" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ216" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA216" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB216" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC216" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD216" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BE216" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF216" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BG216" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BH216" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BI216" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BJ216" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BK216" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BL216" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BM216" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BN216" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BO216" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BP216" t="n">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="n">
+        <v>216</v>
+      </c>
+      <c r="B217" t="n">
+        <v>8227875</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Germany 2. Bundesliga</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="n">
+        <v>46082.39583333334</v>
+      </c>
+      <c r="F217" t="n">
+        <v>24</v>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Eintracht Braunschweig</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Preußen Münster</t>
+        </is>
+      </c>
+      <c r="I217" t="n">
+        <v>0</v>
+      </c>
+      <c r="J217" t="n">
+        <v>0</v>
+      </c>
+      <c r="K217" t="n">
+        <v>0</v>
+      </c>
+      <c r="L217" t="n">
+        <v>1</v>
+      </c>
+      <c r="M217" t="n">
+        <v>2</v>
+      </c>
+      <c r="N217" t="n">
+        <v>3</v>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>['56']</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>['71', '74']</t>
+        </is>
+      </c>
+      <c r="Q217" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R217" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S217" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T217" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U217" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V217" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="W217" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X217" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="Y217" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z217" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AA217" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AB217" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AC217" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD217" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE217" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF217" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG217" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AH217" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI217" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ217" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AK217" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM217" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN217" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AO217" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AP217" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AQ217" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AR217" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AS217" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AT217" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AU217" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV217" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW217" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX217" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY217" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ217" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA217" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB217" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC217" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD217" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BE217" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF217" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BG217" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH217" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BI217" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BJ217" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BK217" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BL217" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BM217" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BN217" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BO217" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BP217" t="n">
+        <v>1.42</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Germany 2. Bundesliga_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Germany 2. Bundesliga_20252026.xlsx
@@ -46494,16 +46494,16 @@
         <v>5</v>
       </c>
       <c r="AW211" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX211" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY211" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ211" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA211" t="n">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/Germany 2. Bundesliga_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Germany 2. Bundesliga_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP217"/>
+  <dimension ref="A1:BP222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AQ2" t="n">
         <v>1.64</v>
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ4" t="n">
         <v>0.83</v>
@@ -1565,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -1783,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ6" t="n">
         <v>0.67</v>
@@ -2004,7 +2004,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
         <v>0.58</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ11" t="n">
         <v>1.25</v>
@@ -3530,7 +3530,7 @@
         <v>1</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -4402,7 +4402,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR18" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ20" t="n">
         <v>1.09</v>
@@ -5274,7 +5274,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR22" t="n">
         <v>1.71</v>
@@ -5489,10 +5489,10 @@
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR23" t="n">
         <v>1.05</v>
@@ -5710,7 +5710,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR24" t="n">
         <v>1.47</v>
@@ -5925,7 +5925,7 @@
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AQ25" t="n">
         <v>0.83</v>
@@ -6364,7 +6364,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR27" t="n">
         <v>1.15</v>
@@ -6579,7 +6579,7 @@
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ28" t="n">
         <v>1.64</v>
@@ -6797,7 +6797,7 @@
         <v>1</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ29" t="n">
         <v>1.75</v>
@@ -7454,7 +7454,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR32" t="n">
         <v>0.99</v>
@@ -8759,7 +8759,7 @@
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ38" t="n">
         <v>0.83</v>
@@ -8980,7 +8980,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR39" t="n">
         <v>1.57</v>
@@ -9413,10 +9413,10 @@
         <v>1.5</v>
       </c>
       <c r="AP41" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR41" t="n">
         <v>1.86</v>
@@ -9631,10 +9631,10 @@
         <v>1.5</v>
       </c>
       <c r="AP42" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR42" t="n">
         <v>1.65</v>
@@ -10067,7 +10067,7 @@
         <v>1.5</v>
       </c>
       <c r="AP44" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ44" t="n">
         <v>1.08</v>
@@ -10506,7 +10506,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR46" t="n">
         <v>1.1</v>
@@ -11811,7 +11811,7 @@
         <v>0</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ52" t="n">
         <v>0.83</v>
@@ -12683,7 +12683,7 @@
         <v>2</v>
       </c>
       <c r="AP56" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AQ56" t="n">
         <v>0.83</v>
@@ -12901,7 +12901,7 @@
         <v>1.33</v>
       </c>
       <c r="AP57" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ57" t="n">
         <v>1.08</v>
@@ -13119,10 +13119,10 @@
         <v>2</v>
       </c>
       <c r="AP58" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR58" t="n">
         <v>1.74</v>
@@ -13340,7 +13340,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ59" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR59" t="n">
         <v>1.39</v>
@@ -13555,7 +13555,7 @@
         <v>1</v>
       </c>
       <c r="AP60" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ60" t="n">
         <v>1.09</v>
@@ -13776,7 +13776,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ61" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR61" t="n">
         <v>1.89</v>
@@ -13994,7 +13994,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ62" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR62" t="n">
         <v>1.42</v>
@@ -14212,7 +14212,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ63" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR63" t="n">
         <v>2.11</v>
@@ -14427,7 +14427,7 @@
         <v>1.33</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ64" t="n">
         <v>1.64</v>
@@ -16610,7 +16610,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ74" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR74" t="n">
         <v>1.36</v>
@@ -17043,10 +17043,10 @@
         <v>1.33</v>
       </c>
       <c r="AP76" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ76" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR76" t="n">
         <v>1.89</v>
@@ -17915,10 +17915,10 @@
         <v>1.5</v>
       </c>
       <c r="AP80" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ80" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR80" t="n">
         <v>1.57</v>
@@ -18133,7 +18133,7 @@
         <v>1.5</v>
       </c>
       <c r="AP81" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ81" t="n">
         <v>0.83</v>
@@ -18351,10 +18351,10 @@
         <v>0.75</v>
       </c>
       <c r="AP82" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ82" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR82" t="n">
         <v>1.6</v>
@@ -18787,7 +18787,7 @@
         <v>1.75</v>
       </c>
       <c r="AP84" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AQ84" t="n">
         <v>1.25</v>
@@ -19662,7 +19662,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ88" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR88" t="n">
         <v>1.29</v>
@@ -20534,7 +20534,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ92" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR92" t="n">
         <v>1.38</v>
@@ -20749,7 +20749,7 @@
         <v>2.2</v>
       </c>
       <c r="AP93" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ93" t="n">
         <v>1.92</v>
@@ -21403,10 +21403,10 @@
         <v>1.2</v>
       </c>
       <c r="AP96" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ96" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR96" t="n">
         <v>1.61</v>
@@ -21621,10 +21621,10 @@
         <v>1</v>
       </c>
       <c r="AP97" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ97" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR97" t="n">
         <v>1.58</v>
@@ -22060,7 +22060,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ99" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR99" t="n">
         <v>1.84</v>
@@ -22275,7 +22275,7 @@
         <v>1.2</v>
       </c>
       <c r="AP100" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ100" t="n">
         <v>0.83</v>
@@ -23365,7 +23365,7 @@
         <v>1.8</v>
       </c>
       <c r="AP105" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AQ105" t="n">
         <v>1.77</v>
@@ -24022,7 +24022,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ108" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR108" t="n">
         <v>1.67</v>
@@ -24676,7 +24676,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ111" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR111" t="n">
         <v>1.33</v>
@@ -24891,7 +24891,7 @@
         <v>2</v>
       </c>
       <c r="AP112" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ112" t="n">
         <v>1.92</v>
@@ -25112,7 +25112,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ113" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR113" t="n">
         <v>1.37</v>
@@ -25545,7 +25545,7 @@
         <v>1</v>
       </c>
       <c r="AP115" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ115" t="n">
         <v>0.83</v>
@@ -25981,10 +25981,10 @@
         <v>1</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ117" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR117" t="n">
         <v>1.44</v>
@@ -26202,7 +26202,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ118" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR118" t="n">
         <v>1.84</v>
@@ -26635,7 +26635,7 @@
         <v>2.33</v>
       </c>
       <c r="AP120" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AQ120" t="n">
         <v>1.75</v>
@@ -27725,7 +27725,7 @@
         <v>1.67</v>
       </c>
       <c r="AP125" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ125" t="n">
         <v>1.25</v>
@@ -28164,7 +28164,7 @@
         <v>1</v>
       </c>
       <c r="AQ127" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR127" t="n">
         <v>1.24</v>
@@ -28818,7 +28818,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ130" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR130" t="n">
         <v>2.01</v>
@@ -29033,7 +29033,7 @@
         <v>1.71</v>
       </c>
       <c r="AP131" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ131" t="n">
         <v>1.77</v>
@@ -29469,7 +29469,7 @@
         <v>0.86</v>
       </c>
       <c r="AP133" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ133" t="n">
         <v>1</v>
@@ -29690,7 +29690,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ134" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR134" t="n">
         <v>1.39</v>
@@ -29905,7 +29905,7 @@
         <v>0.86</v>
       </c>
       <c r="AP135" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ135" t="n">
         <v>0.83</v>
@@ -30126,7 +30126,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ136" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR136" t="n">
         <v>1.27</v>
@@ -30562,7 +30562,7 @@
         <v>1</v>
       </c>
       <c r="AQ138" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR138" t="n">
         <v>1.3</v>
@@ -31216,7 +31216,7 @@
         <v>0.58</v>
       </c>
       <c r="AQ141" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR141" t="n">
         <v>1.71</v>
@@ -31649,7 +31649,7 @@
         <v>0.86</v>
       </c>
       <c r="AP143" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ143" t="n">
         <v>0.92</v>
@@ -31867,7 +31867,7 @@
         <v>1</v>
       </c>
       <c r="AP144" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AQ144" t="n">
         <v>0.67</v>
@@ -32085,10 +32085,10 @@
         <v>1.29</v>
       </c>
       <c r="AP145" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ145" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR145" t="n">
         <v>1.74</v>
@@ -32303,7 +32303,7 @@
         <v>1.57</v>
       </c>
       <c r="AP146" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ146" t="n">
         <v>1.25</v>
@@ -32524,7 +32524,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ147" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR147" t="n">
         <v>1.45</v>
@@ -32742,7 +32742,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ148" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR148" t="n">
         <v>1.91</v>
@@ -33829,7 +33829,7 @@
         <v>2</v>
       </c>
       <c r="AP153" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ153" t="n">
         <v>1.92</v>
@@ -34268,7 +34268,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ155" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR155" t="n">
         <v>1.38</v>
@@ -34486,7 +34486,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ156" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR156" t="n">
         <v>1.35</v>
@@ -34919,7 +34919,7 @@
         <v>1.78</v>
       </c>
       <c r="AP158" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ158" t="n">
         <v>1.77</v>
@@ -36230,7 +36230,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ164" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR164" t="n">
         <v>1.52</v>
@@ -36445,7 +36445,7 @@
         <v>0.88</v>
       </c>
       <c r="AP165" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ165" t="n">
         <v>0.67</v>
@@ -36666,7 +36666,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ166" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR166" t="n">
         <v>1.23</v>
@@ -36884,7 +36884,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ167" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR167" t="n">
         <v>1.99</v>
@@ -37535,7 +37535,7 @@
         <v>0.75</v>
       </c>
       <c r="AP170" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ170" t="n">
         <v>0.92</v>
@@ -37753,7 +37753,7 @@
         <v>0.89</v>
       </c>
       <c r="AP171" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ171" t="n">
         <v>0.83</v>
@@ -37971,7 +37971,7 @@
         <v>1</v>
       </c>
       <c r="AP172" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AQ172" t="n">
         <v>1.09</v>
@@ -38407,7 +38407,7 @@
         <v>0.67</v>
       </c>
       <c r="AP174" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ174" t="n">
         <v>0.92</v>
@@ -39500,7 +39500,7 @@
         <v>1</v>
       </c>
       <c r="AQ179" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR179" t="n">
         <v>1.33</v>
@@ -40154,7 +40154,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ182" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR182" t="n">
         <v>1.14</v>
@@ -40587,7 +40587,7 @@
         <v>0.78</v>
       </c>
       <c r="AP184" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ184" t="n">
         <v>0.67</v>
@@ -40805,7 +40805,7 @@
         <v>1.67</v>
       </c>
       <c r="AP185" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ185" t="n">
         <v>1.64</v>
@@ -41023,7 +41023,7 @@
         <v>1.1</v>
       </c>
       <c r="AP186" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AQ186" t="n">
         <v>1.08</v>
@@ -41241,7 +41241,7 @@
         <v>1</v>
       </c>
       <c r="AP187" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ187" t="n">
         <v>1.09</v>
@@ -41462,7 +41462,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ188" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR188" t="n">
         <v>1.38</v>
@@ -41680,7 +41680,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ189" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR189" t="n">
         <v>1.55</v>
@@ -41898,7 +41898,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ190" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR190" t="n">
         <v>1.92</v>
@@ -42113,7 +42113,7 @@
         <v>0.91</v>
       </c>
       <c r="AP191" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ191" t="n">
         <v>1</v>
@@ -43642,7 +43642,7 @@
         <v>0.58</v>
       </c>
       <c r="AQ198" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR198" t="n">
         <v>1.75</v>
@@ -44078,7 +44078,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ200" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR200" t="n">
         <v>1.17</v>
@@ -44511,10 +44511,10 @@
         <v>1</v>
       </c>
       <c r="AP202" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ202" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR202" t="n">
         <v>1.82</v>
@@ -44729,10 +44729,10 @@
         <v>1</v>
       </c>
       <c r="AP203" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ203" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AR203" t="n">
         <v>1.74</v>
@@ -44950,7 +44950,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ204" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR204" t="n">
         <v>1.35</v>
@@ -45165,10 +45165,10 @@
         <v>1.45</v>
       </c>
       <c r="AP205" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AQ205" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR205" t="n">
         <v>1.56</v>
@@ -45601,7 +45601,7 @@
         <v>1.8</v>
       </c>
       <c r="AP207" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ207" t="n">
         <v>1.64</v>
@@ -47860,6 +47860,1096 @@
       </c>
       <c r="BP217" t="n">
         <v>1.42</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="n">
+        <v>217</v>
+      </c>
+      <c r="B218" t="n">
+        <v>8228049</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Germany 2. Bundesliga</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="n">
+        <v>46087.60416666666</v>
+      </c>
+      <c r="F218" t="n">
+        <v>25</v>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Elversberg</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Magdeburg</t>
+        </is>
+      </c>
+      <c r="I218" t="n">
+        <v>0</v>
+      </c>
+      <c r="J218" t="n">
+        <v>0</v>
+      </c>
+      <c r="K218" t="n">
+        <v>0</v>
+      </c>
+      <c r="L218" t="n">
+        <v>1</v>
+      </c>
+      <c r="M218" t="n">
+        <v>0</v>
+      </c>
+      <c r="N218" t="n">
+        <v>1</v>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>['85']</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q218" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="R218" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S218" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T218" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U218" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V218" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W218" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="X218" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Y218" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z218" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AA218" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB218" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AC218" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD218" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE218" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF218" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="AG218" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH218" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AI218" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AJ218" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AK218" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AL218" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM218" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AN218" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO218" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AP218" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AQ218" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AR218" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AS218" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AT218" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AU218" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV218" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW218" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX218" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY218" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ218" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA218" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB218" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC218" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD218" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BE218" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF218" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BG218" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH218" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BI218" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BJ218" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK218" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BL218" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BM218" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BN218" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BO218" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="BP218" t="n">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="n">
+        <v>218</v>
+      </c>
+      <c r="B219" t="n">
+        <v>8227984</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Germany 2. Bundesliga</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="n">
+        <v>46087.60416666666</v>
+      </c>
+      <c r="F219" t="n">
+        <v>25</v>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Schalke 04</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Arminia Bielefeld</t>
+        </is>
+      </c>
+      <c r="I219" t="n">
+        <v>1</v>
+      </c>
+      <c r="J219" t="n">
+        <v>0</v>
+      </c>
+      <c r="K219" t="n">
+        <v>1</v>
+      </c>
+      <c r="L219" t="n">
+        <v>1</v>
+      </c>
+      <c r="M219" t="n">
+        <v>0</v>
+      </c>
+      <c r="N219" t="n">
+        <v>1</v>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>['15']</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q219" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="R219" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S219" t="n">
+        <v>4</v>
+      </c>
+      <c r="T219" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="U219" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="V219" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W219" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X219" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y219" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z219" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA219" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB219" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AC219" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD219" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE219" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF219" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AG219" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AH219" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AI219" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ219" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK219" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM219" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AN219" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AO219" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AP219" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AQ219" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AR219" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AS219" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AT219" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AU219" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV219" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW219" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX219" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY219" t="n">
+        <v>24</v>
+      </c>
+      <c r="AZ219" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA219" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB219" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC219" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD219" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BE219" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF219" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BG219" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BH219" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BI219" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BJ219" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BK219" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BL219" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BM219" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BN219" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BO219" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BP219" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="n">
+        <v>219</v>
+      </c>
+      <c r="B220" t="n">
+        <v>8227982</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Germany 2. Bundesliga</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="n">
+        <v>46088.375</v>
+      </c>
+      <c r="F220" t="n">
+        <v>25</v>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Darmstadt 98</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Holstein Kiel</t>
+        </is>
+      </c>
+      <c r="I220" t="n">
+        <v>0</v>
+      </c>
+      <c r="J220" t="n">
+        <v>0</v>
+      </c>
+      <c r="K220" t="n">
+        <v>0</v>
+      </c>
+      <c r="L220" t="n">
+        <v>2</v>
+      </c>
+      <c r="M220" t="n">
+        <v>0</v>
+      </c>
+      <c r="N220" t="n">
+        <v>2</v>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>['48', '52']</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q220" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R220" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="S220" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="T220" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="U220" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="V220" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="W220" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X220" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="Y220" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z220" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA220" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB220" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AC220" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD220" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="AE220" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF220" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="AG220" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH220" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AI220" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ220" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AK220" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL220" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM220" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AN220" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AO220" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AP220" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AQ220" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AR220" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AS220" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AT220" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AU220" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV220" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW220" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX220" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY220" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ220" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA220" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB220" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC220" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD220" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BE220" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF220" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BG220" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BH220" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI220" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BJ220" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BK220" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BL220" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BM220" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BN220" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BO220" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BP220" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="B221" t="n">
+        <v>8227983</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Germany 2. Bundesliga</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="n">
+        <v>46088.375</v>
+      </c>
+      <c r="F221" t="n">
+        <v>25</v>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Nürnberg</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Fortuna Düsseldorf</t>
+        </is>
+      </c>
+      <c r="I221" t="n">
+        <v>0</v>
+      </c>
+      <c r="J221" t="n">
+        <v>0</v>
+      </c>
+      <c r="K221" t="n">
+        <v>0</v>
+      </c>
+      <c r="L221" t="n">
+        <v>0</v>
+      </c>
+      <c r="M221" t="n">
+        <v>1</v>
+      </c>
+      <c r="N221" t="n">
+        <v>1</v>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>['53']</t>
+        </is>
+      </c>
+      <c r="Q221" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R221" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="S221" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="T221" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U221" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="V221" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="W221" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X221" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Y221" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z221" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA221" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB221" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AC221" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD221" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="AE221" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AF221" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AG221" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH221" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AI221" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AJ221" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AK221" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM221" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN221" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO221" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AP221" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AQ221" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AR221" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AS221" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AT221" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU221" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV221" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW221" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX221" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY221" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ221" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA221" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB221" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC221" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD221" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE221" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF221" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BG221" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH221" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BI221" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BJ221" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BK221" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BL221" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BM221" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="BN221" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BO221" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BP221" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="n">
+        <v>221</v>
+      </c>
+      <c r="B222" t="n">
+        <v>8227987</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Germany 2. Bundesliga</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="n">
+        <v>46088.375</v>
+      </c>
+      <c r="F222" t="n">
+        <v>25</v>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Paderborn</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Eintracht Braunschweig</t>
+        </is>
+      </c>
+      <c r="I222" t="n">
+        <v>0</v>
+      </c>
+      <c r="J222" t="n">
+        <v>0</v>
+      </c>
+      <c r="K222" t="n">
+        <v>0</v>
+      </c>
+      <c r="L222" t="n">
+        <v>1</v>
+      </c>
+      <c r="M222" t="n">
+        <v>1</v>
+      </c>
+      <c r="N222" t="n">
+        <v>2</v>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>['90+8']</t>
+        </is>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>['52']</t>
+        </is>
+      </c>
+      <c r="Q222" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="R222" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S222" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="T222" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="U222" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V222" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="W222" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X222" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="Y222" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z222" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AA222" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AB222" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AC222" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD222" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="AE222" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF222" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AG222" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH222" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AI222" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AJ222" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AK222" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AL222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM222" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AN222" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AO222" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AP222" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ222" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AR222" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AS222" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AT222" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AU222" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV222" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW222" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX222" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY222" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ222" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA222" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB222" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC222" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD222" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BE222" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF222" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="BG222" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH222" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI222" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BJ222" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BK222" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BL222" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BM222" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BN222" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BO222" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BP222" t="n">
+        <v>1.44</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Germany 2. Bundesliga_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Germany 2. Bundesliga_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP222"/>
+  <dimension ref="A1:BP223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2658,7 +2658,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ17" t="n">
         <v>1.77</v>
@@ -4838,7 +4838,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR20" t="n">
         <v>1.37</v>
@@ -7669,7 +7669,7 @@
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ33" t="n">
         <v>0.92</v>
@@ -10288,7 +10288,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR45" t="n">
         <v>1.27</v>
@@ -13558,7 +13558,7 @@
         <v>2</v>
       </c>
       <c r="AQ60" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR60" t="n">
         <v>1.62</v>
@@ -13773,7 +13773,7 @@
         <v>2</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ61" t="n">
         <v>1.08</v>
@@ -17482,7 +17482,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ78" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR78" t="n">
         <v>1.51</v>
@@ -17697,7 +17697,7 @@
         <v>1.75</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ79" t="n">
         <v>1.64</v>
@@ -21842,7 +21842,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR98" t="n">
         <v>1.4</v>
@@ -22057,7 +22057,7 @@
         <v>0.8</v>
       </c>
       <c r="AP99" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ99" t="n">
         <v>1.23</v>
@@ -24455,7 +24455,7 @@
         <v>0.83</v>
       </c>
       <c r="AP110" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ110" t="n">
         <v>1.08</v>
@@ -27074,7 +27074,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ122" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR122" t="n">
         <v>1.18</v>
@@ -28815,7 +28815,7 @@
         <v>0.83</v>
       </c>
       <c r="AP130" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ130" t="n">
         <v>0.77</v>
@@ -30780,7 +30780,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ139" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR139" t="n">
         <v>1.53</v>
@@ -33175,7 +33175,7 @@
         <v>0.75</v>
       </c>
       <c r="AP150" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ150" t="n">
         <v>1</v>
@@ -35573,7 +35573,7 @@
         <v>1.5</v>
       </c>
       <c r="AP161" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ161" t="n">
         <v>1.25</v>
@@ -37974,7 +37974,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ172" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR172" t="n">
         <v>1.52</v>
@@ -38625,7 +38625,7 @@
         <v>1.7</v>
       </c>
       <c r="AP175" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ175" t="n">
         <v>1.62</v>
@@ -41244,7 +41244,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ187" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR187" t="n">
         <v>1.73</v>
@@ -43857,7 +43857,7 @@
         <v>1.7</v>
       </c>
       <c r="AP199" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ199" t="n">
         <v>1.75</v>
@@ -44293,7 +44293,7 @@
         <v>0.7</v>
       </c>
       <c r="AP201" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ201" t="n">
         <v>0.67</v>
@@ -45822,7 +45822,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ208" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR208" t="n">
         <v>1.44</v>
@@ -48950,6 +48950,224 @@
       </c>
       <c r="BP222" t="n">
         <v>1.44</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="1" t="n">
+        <v>222</v>
+      </c>
+      <c r="B223" t="n">
+        <v>8227988</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Germany 2. Bundesliga</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="n">
+        <v>46088.6875</v>
+      </c>
+      <c r="F223" t="n">
+        <v>25</v>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Bochum</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Kaiserslautern</t>
+        </is>
+      </c>
+      <c r="I223" t="n">
+        <v>1</v>
+      </c>
+      <c r="J223" t="n">
+        <v>1</v>
+      </c>
+      <c r="K223" t="n">
+        <v>2</v>
+      </c>
+      <c r="L223" t="n">
+        <v>3</v>
+      </c>
+      <c r="M223" t="n">
+        <v>2</v>
+      </c>
+      <c r="N223" t="n">
+        <v>5</v>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>['9', '66', '69']</t>
+        </is>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>['30', '50']</t>
+        </is>
+      </c>
+      <c r="Q223" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="R223" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="S223" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="T223" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="U223" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="V223" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="W223" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X223" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="Y223" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z223" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AA223" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB223" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AC223" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD223" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="AE223" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF223" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AG223" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AH223" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AI223" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AJ223" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AK223" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AL223" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM223" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AN223" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AO223" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AP223" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AQ223" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR223" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS223" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AT223" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AU223" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV223" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW223" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX223" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY223" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ223" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA223" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB223" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC223" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD223" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BE223" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF223" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BG223" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH223" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI223" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ223" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BK223" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BL223" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BM223" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BN223" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BO223" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BP223" t="n">
+        <v>1.41</v>
       </c>
     </row>
   </sheetData>
